--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1,20 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="19635" windowHeight="7500" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha2" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Planilha3" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Planilha2" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha3" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -23,171 +30,972 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t xml:space="preserve">FardaoColhido</t>
+    <t>FardaoColhido</t>
   </si>
   <si>
-    <t xml:space="preserve">Beneficiado</t>
+    <t>Beneficiado</t>
   </si>
   <si>
-    <t xml:space="preserve">InicioBeneficio</t>
+    <t>InicioBeneficio</t>
   </si>
   <si>
-    <t xml:space="preserve">Vinculadas</t>
+    <t>Vinculadas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;* #,##0_-;\-&quot;R$&quot;* #,##0_-;_-&quot;R$&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="0"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="9">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Moeda" xfId="2" builtinId="4"/>
+    <cellStyle name="Porcentagem" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Moeda [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Hyperlink seguido" xfId="7" builtinId="9"/>
+    <cellStyle name="Observação" xfId="8" builtinId="10"/>
+    <cellStyle name="Texto de Aviso" xfId="9" builtinId="11"/>
+    <cellStyle name="Título" xfId="10" builtinId="15"/>
+    <cellStyle name="Texto Explicativo" xfId="11" builtinId="53"/>
+    <cellStyle name="Título 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Título 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Título 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Título 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Entrada" xfId="16" builtinId="20"/>
+    <cellStyle name="Saída" xfId="17" builtinId="21"/>
+    <cellStyle name="Cálculo" xfId="18" builtinId="22"/>
+    <cellStyle name="Célula de Verificação" xfId="19" builtinId="23"/>
+    <cellStyle name="Célula Vinculada" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Bom" xfId="22" builtinId="26"/>
+    <cellStyle name="Ruim" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutro" xfId="24" builtinId="28"/>
+    <cellStyle name="Ênfase 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Ênfase 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Ênfase 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Ênfase 1" xfId="28" builtinId="32"/>
+    <cellStyle name="Ênfase 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Ênfase 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Ênfase 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Ênfase 2" xfId="32" builtinId="36"/>
+    <cellStyle name="Ênfase 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Ênfase 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Ênfase 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Ênfase 3" xfId="36" builtinId="40"/>
+    <cellStyle name="Ênfase 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Ênfase 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Ênfase 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Ênfase 4" xfId="40" builtinId="44"/>
+    <cellStyle name="Ênfase 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Ênfase 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Ênfase 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Ênfase 5" xfId="44" builtinId="48"/>
+    <cellStyle name="Ênfase 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Ênfase 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Ênfase 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Ênfase 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -214,7 +1022,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -238,7 +1046,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -298,26 +1106,25 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelRow="1" outlineLevelCol="2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.11"/>
+    <col min="1" max="1" width="14.1142857142857" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -328,23 +1135,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+    <row r="2" customHeight="1" spans="1:3">
+      <c r="A2" s="1">
         <v>11278</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <f aca="false">Planilha3!B1</f>
-        <v>6534</v>
+      <c r="B2" s="1">
+        <f>Planilha3!B1</f>
+        <v>6648</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="2">
         <v>45867</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
@@ -352,37 +1158,39 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelRow="3" outlineLevelCol="1"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" ht="12.75" spans="1:2">
+      <c r="A1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="0" t="n">
-        <f aca="false">SUM(A2:A36)</f>
-        <v>6534</v>
+      <c r="B1">
+        <f>SUM(A2:A36)</f>
+        <v>6648</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+    <row r="2" customHeight="1" spans="1:1">
+      <c r="A2" s="1">
         <v>6416</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+    <row r="3" customHeight="1" spans="1:1">
+      <c r="A3">
         <v>118</v>
       </c>
     </row>
+    <row r="4" customHeight="1" spans="1:1">
+      <c r="A4">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7500" tabRatio="500"/>
+    <workbookView windowWidth="19635" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="1" r:id="rId1"/>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>6648</v>
+        <v>6755</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,8 +1160,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelRow="3" outlineLevelCol="1"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
       <c r="A1" t="s">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>6648</v>
+        <v>6755</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1187,6 +1187,11 @@
         <v>114</v>
       </c>
     </row>
+    <row r="5" customHeight="1" spans="1:1">
+      <c r="A5">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>6755</v>
+        <v>6865</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,8 +1160,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelRow="4" outlineLevelCol="1"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelRow="5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
       <c r="A1" t="s">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>6755</v>
+        <v>6865</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1192,6 +1192,11 @@
         <v>107</v>
       </c>
     </row>
+    <row r="6" customHeight="1" spans="1:1">
+      <c r="A6">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>6865</v>
+        <v>6982</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,8 +1160,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelRow="5" outlineLevelCol="1"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelRow="6" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
       <c r="A1" t="s">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>6865</v>
+        <v>6982</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1195,6 +1195,11 @@
     <row r="6" customHeight="1" spans="1:1">
       <c r="A6">
         <v>110</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:1">
+      <c r="A7">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>6982</v>
+        <v>7088</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,8 +1160,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelRow="6" outlineLevelCol="1"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelRow="7" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
       <c r="A1" t="s">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>6982</v>
+        <v>7088</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1200,6 +1200,11 @@
     <row r="7" customHeight="1" spans="1:1">
       <c r="A7">
         <v>117</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:1">
+      <c r="A8">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>7088</v>
+        <v>7192</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,8 +1160,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelRow="7" outlineLevelCol="1"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
       <c r="A1" t="s">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>7088</v>
+        <v>7192</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1205,6 +1205,11 @@
     <row r="8" customHeight="1" spans="1:1">
       <c r="A8">
         <v>106</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:1">
+      <c r="A9">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>7192</v>
+        <v>7291</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,7 +1160,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>7192</v>
+        <v>7291</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1210,6 +1210,11 @@
     <row r="9" customHeight="1" spans="1:1">
       <c r="A9">
         <v>104</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:1">
+      <c r="A10">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>7291</v>
+        <v>7409</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,7 +1160,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>7291</v>
+        <v>7409</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1215,6 +1215,11 @@
     <row r="10" customHeight="1" spans="1:1">
       <c r="A10">
         <v>99</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:1">
+      <c r="A11">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>7409</v>
+        <v>7497</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,7 +1160,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>7409</v>
+        <v>7497</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1220,6 +1220,11 @@
     <row r="11" customHeight="1" spans="1:1">
       <c r="A11">
         <v>118</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:1">
+      <c r="A12">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>7497</v>
+        <v>7605</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,7 +1160,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>7497</v>
+        <v>7605</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1225,6 +1225,11 @@
     <row r="12" customHeight="1" spans="1:1">
       <c r="A12">
         <v>88</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:1">
+      <c r="A13">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>7605</v>
+        <v>7718</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,7 +1160,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>7605</v>
+        <v>7718</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1230,6 +1230,11 @@
     <row r="13" customHeight="1" spans="1:1">
       <c r="A13">
         <v>108</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:1">
+      <c r="A14">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>7718</v>
+        <v>7836</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,7 +1160,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>7718</v>
+        <v>7836</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1235,6 +1235,11 @@
     <row r="14" customHeight="1" spans="1:1">
       <c r="A14">
         <v>113</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:1">
+      <c r="A15">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>7836</v>
+        <v>7906</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,7 +1160,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>7836</v>
+        <v>7906</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1240,6 +1240,11 @@
     <row r="15" customHeight="1" spans="1:1">
       <c r="A15">
         <v>118</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:1">
+      <c r="A16">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>7906</v>
+        <v>7981</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,7 +1160,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>7906</v>
+        <v>7981</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1245,6 +1245,11 @@
     <row r="16" customHeight="1" spans="1:1">
       <c r="A16">
         <v>70</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:1">
+      <c r="A17">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>7981</v>
+        <v>8090</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,7 +1160,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>7981</v>
+        <v>8090</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1250,6 +1250,11 @@
     <row r="17" customHeight="1" spans="1:1">
       <c r="A17">
         <v>75</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:1">
+      <c r="A18">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>8090</v>
+        <v>8219</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,7 +1160,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>8090</v>
+        <v>8219</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1255,6 +1255,11 @@
     <row r="18" customHeight="1" spans="1:1">
       <c r="A18">
         <v>109</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:1">
+      <c r="A19">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>8219</v>
+        <v>8344</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,7 +1160,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>8219</v>
+        <v>8344</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1260,6 +1260,11 @@
     <row r="19" customHeight="1" spans="1:1">
       <c r="A19">
         <v>129</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:1">
+      <c r="A20">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>8344</v>
+        <v>8485</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,7 +1160,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>8344</v>
+        <v>8485</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1265,6 +1265,11 @@
     <row r="20" customHeight="1" spans="1:1">
       <c r="A20">
         <v>125</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:1">
+      <c r="A21">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B2" s="1">
         <f>Planilha3!B1</f>
-        <v>8485</v>
+        <v>8612</v>
       </c>
       <c r="C2" s="2">
         <v>45867</v>
@@ -1160,7 +1160,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" ht="12.75" spans="1:2">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B1">
         <f>SUM(A2:A36)</f>
-        <v>8485</v>
+        <v>8612</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1270,6 +1270,11 @@
     <row r="21" customHeight="1" spans="1:1">
       <c r="A21">
         <v>141</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:1">
+      <c r="A22">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -657,9 +657,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1121,29 +1130,29 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelRow="1" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="14.1142857142857" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1142857142857" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:3">
-      <c r="A2" s="1">
+      <c r="A2" s="4">
         <v>11278</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>8612</v>
-      </c>
-      <c r="C2" s="2">
+        <v>8744</v>
+      </c>
+      <c r="C2" s="5">
         <v>45867</v>
       </c>
     </row>
@@ -1160,121 +1169,129 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="12.6761904761905" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="12.75" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1">
-        <f>SUM(A2:A36)</f>
-        <v>8612</v>
+      <c r="B1" s="2">
+        <f>SUM(A2:A54)</f>
+        <v>8744</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
-      <c r="A2" s="1">
+      <c r="A2" s="3">
         <v>6416</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:1">
-      <c r="A3">
+      <c r="A3" s="1">
         <v>118</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:1">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>114</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:1">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>107</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:1">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>110</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:1">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>117</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:1">
-      <c r="A8">
+      <c r="A8" s="1">
         <v>106</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:1">
-      <c r="A9">
+      <c r="A9" s="1">
         <v>104</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:1">
-      <c r="A10">
+      <c r="A10" s="1">
         <v>99</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:1">
-      <c r="A11">
+      <c r="A11" s="1">
         <v>118</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:1">
-      <c r="A12">
+      <c r="A12" s="1">
         <v>88</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:1">
-      <c r="A13">
+      <c r="A13" s="1">
         <v>108</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:1">
-      <c r="A14">
+      <c r="A14" s="1">
         <v>113</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:1">
-      <c r="A15">
+      <c r="A15" s="1">
         <v>118</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:1">
-      <c r="A16">
+      <c r="A16" s="1">
         <v>70</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:1">
-      <c r="A17">
+      <c r="A17" s="1">
         <v>75</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:1">
-      <c r="A18">
+      <c r="A18" s="1">
         <v>109</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:1">
-      <c r="A19">
+      <c r="A19" s="1">
         <v>129</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:1">
-      <c r="A20">
+      <c r="A20" s="1">
         <v>125</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:1">
-      <c r="A21">
+      <c r="A21" s="1">
         <v>141</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:1">
-      <c r="A22">
+      <c r="A22" s="1">
         <v>127</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:1">
+      <c r="A23" s="1">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>8744</v>
+        <v>8872</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,19 +1169,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" ht="12.75" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>8744</v>
+        <v>8872</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1292,6 +1292,11 @@
     <row r="23" customHeight="1" spans="1:1">
       <c r="A23" s="1">
         <v>132</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:1">
+      <c r="A24" s="1">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>8872</v>
+        <v>8996</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>8872</v>
+        <v>8996</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1297,6 +1297,11 @@
     <row r="24" customHeight="1" spans="1:1">
       <c r="A24" s="1">
         <v>128</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:1">
+      <c r="A25" s="1">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>8996</v>
+        <v>9127</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>8996</v>
+        <v>9127</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1302,6 +1302,11 @@
     <row r="25" customHeight="1" spans="1:1">
       <c r="A25" s="1">
         <v>124</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:1">
+      <c r="A26" s="1">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>9127</v>
+        <v>9263</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>9127</v>
+        <v>9263</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1307,6 +1307,11 @@
     <row r="26" customHeight="1" spans="1:1">
       <c r="A26" s="1">
         <v>131</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:1">
+      <c r="A27" s="1">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>9263</v>
+        <v>9363</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>9263</v>
+        <v>9363</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1312,6 +1312,11 @@
     <row r="27" customHeight="1" spans="1:1">
       <c r="A27" s="1">
         <v>136</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:1">
+      <c r="A28" s="1">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>9363</v>
+        <v>9497</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>9363</v>
+        <v>9497</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1317,6 +1317,11 @@
     <row r="28" customHeight="1" spans="1:1">
       <c r="A28" s="1">
         <v>100</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:1">
+      <c r="A29" s="1">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>9497</v>
+        <v>9608</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>9497</v>
+        <v>9608</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1322,6 +1322,11 @@
     <row r="29" customHeight="1" spans="1:1">
       <c r="A29" s="1">
         <v>134</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:1">
+      <c r="A30" s="1">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>9608</v>
+        <v>9738</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>9608</v>
+        <v>9738</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1327,6 +1327,11 @@
     <row r="30" customHeight="1" spans="1:1">
       <c r="A30" s="1">
         <v>111</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:1">
+      <c r="A31" s="1">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>9738</v>
+        <v>9867</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>9738</v>
+        <v>9867</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1332,6 +1332,11 @@
     <row r="31" customHeight="1" spans="1:1">
       <c r="A31" s="1">
         <v>130</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:1">
+      <c r="A32" s="1">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>9867</v>
+        <v>9996</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>9867</v>
+        <v>9996</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1336,6 +1336,11 @@
     </row>
     <row r="32" customHeight="1" spans="1:1">
       <c r="A32" s="1">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:1">
+      <c r="A33" s="1">
         <v>129</v>
       </c>
     </row>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>9996</v>
+        <v>10160</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>9996</v>
+        <v>10160</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1342,6 +1342,11 @@
     <row r="33" customHeight="1" spans="1:1">
       <c r="A33" s="1">
         <v>129</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:1">
+      <c r="A34" s="1">
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>10160</v>
+        <v>10311</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>10160</v>
+        <v>10311</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1347,6 +1347,11 @@
     <row r="34" customHeight="1" spans="1:1">
       <c r="A34" s="1">
         <v>164</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:1">
+      <c r="A35" s="1">
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>10311</v>
+        <v>10445</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>10311</v>
+        <v>10445</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1352,6 +1352,11 @@
     <row r="35" customHeight="1" spans="1:1">
       <c r="A35" s="1">
         <v>151</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:1">
+      <c r="A36" s="1">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>10445</v>
+        <v>10573</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>10445</v>
+        <v>10573</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1357,6 +1357,11 @@
     <row r="36" customHeight="1" spans="1:1">
       <c r="A36" s="1">
         <v>134</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:1">
+      <c r="A37" s="1">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>10573</v>
+        <v>10700</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>10573</v>
+        <v>10700</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1362,6 +1362,11 @@
     <row r="37" customHeight="1" spans="1:1">
       <c r="A37" s="1">
         <v>128</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:1">
+      <c r="A38" s="1">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>10700</v>
+        <v>10840</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>10700</v>
+        <v>10840</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1367,6 +1367,11 @@
     <row r="38" customHeight="1" spans="1:1">
       <c r="A38" s="1">
         <v>127</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:1">
+      <c r="A39" s="1">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>10840</v>
+        <v>10969</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>10840</v>
+        <v>10969</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1372,6 +1372,11 @@
     <row r="39" customHeight="1" spans="1:1">
       <c r="A39" s="1">
         <v>140</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:1">
+      <c r="A40" s="1">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>10969</v>
+        <v>11088</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>10969</v>
+        <v>11088</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1377,6 +1377,11 @@
     <row r="40" customHeight="1" spans="1:1">
       <c r="A40" s="1">
         <v>129</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:1">
+      <c r="A41" s="1">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>11088</v>
+        <v>11186</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>11088</v>
+        <v>11186</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1382,6 +1382,11 @@
     <row r="41" customHeight="1" spans="1:1">
       <c r="A41" s="1">
         <v>119</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:1">
+      <c r="A42" s="1">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1146,11 +1146,11 @@
     </row>
     <row r="2" customHeight="1" spans="1:3">
       <c r="A2" s="4">
-        <v>11278</v>
+        <v>11286</v>
       </c>
       <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v>11186</v>
+        <v>11286</v>
       </c>
       <c r="C2" s="5">
         <v>45867</v>
@@ -1169,7 +1169,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.6761904761905" style="1"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B1" s="2">
         <f>SUM(A2:A54)</f>
-        <v>11186</v>
+        <v>11286</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:1">
@@ -1387,6 +1387,11 @@
     <row r="42" customHeight="1" spans="1:1">
       <c r="A42" s="1">
         <v>98</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:1">
+      <c r="A43" s="1">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12180" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="1" r:id="rId1"/>
@@ -53,9 +53,23 @@
     <numFmt numFmtId="179" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -522,159 +536,171 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1130,31 +1156,28 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelRow="1" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="14.1142857142857" style="4" customWidth="1"/>
+    <col min="1" max="1" width="18.8571428571429" style="6" customWidth="1"/>
+    <col min="2" max="2" width="15.1428571428571" style="7" customWidth="1"/>
+    <col min="3" max="3" width="18.8571428571429" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:3">
-      <c r="A2" s="4">
-        <v>11286</v>
+    <row r="2" customHeight="1" spans="2:3">
+      <c r="B2" s="6" t="str">
+        <f>Planilha3!B1</f>
+        <v/>
       </c>
-      <c r="B2" s="4">
-        <f>Planilha3!B1</f>
-        <v>11286</v>
-      </c>
-      <c r="C2" s="5">
-        <v>45867</v>
-      </c>
+      <c r="C2" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -1169,231 +1192,133 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="12.6761904761905" style="1"/>
+    <col min="1" max="1" width="15.1428571428571" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.14285714285714" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.75" spans="1:2">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="21" spans="1:2">
+      <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="2">
-        <f>SUM(A2:A54)</f>
-        <v>11286</v>
+      <c r="B1" s="4" t="str">
+        <f>IF(A2="","",SUM(A2:A54))</f>
+        <v/>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:1">
-      <c r="A2" s="3">
-        <v>6416</v>
-      </c>
+    <row r="2" ht="18" customHeight="1" spans="1:1">
+      <c r="A2" s="5"/>
     </row>
-    <row r="3" customHeight="1" spans="1:1">
-      <c r="A3" s="1">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:1">
-      <c r="A4" s="1">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:1">
-      <c r="A5" s="1">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:1">
-      <c r="A6" s="1">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:1">
-      <c r="A7" s="1">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:1">
-      <c r="A8" s="1">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:1">
-      <c r="A9" s="1">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:1">
-      <c r="A10" s="1">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:1">
-      <c r="A11" s="1">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:1">
-      <c r="A12" s="1">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:1">
-      <c r="A13" s="1">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:1">
-      <c r="A14" s="1">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:1">
-      <c r="A15" s="1">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:1">
-      <c r="A16" s="1">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:1">
-      <c r="A17" s="1">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:1">
-      <c r="A18" s="1">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:1">
-      <c r="A19" s="1">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:1">
-      <c r="A20" s="1">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:1">
-      <c r="A21" s="1">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:1">
-      <c r="A22" s="1">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:1">
-      <c r="A23" s="1">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:1">
-      <c r="A24" s="1">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:1">
-      <c r="A25" s="1">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:1">
-      <c r="A26" s="1">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:1">
-      <c r="A27" s="1">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:1">
-      <c r="A28" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:1">
-      <c r="A29" s="1">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:1">
-      <c r="A30" s="1">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:1">
-      <c r="A31" s="1">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:1">
-      <c r="A32" s="1">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="1:1">
-      <c r="A33" s="1">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="1:1">
-      <c r="A34" s="1">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:1">
-      <c r="A35" s="1">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="1:1">
-      <c r="A36" s="1">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="1:1">
-      <c r="A37" s="1">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="1:1">
-      <c r="A38" s="1">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="1:1">
-      <c r="A39" s="1">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="1:1">
-      <c r="A40" s="1">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="1:1">
-      <c r="A41" s="1">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="1:1">
-      <c r="A42" s="1">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="1:1">
-      <c r="A43" s="1">
-        <v>100</v>
-      </c>
-    </row>
+    <row r="3" ht="15" customHeight="1"/>
+    <row r="4" ht="15" customHeight="1"/>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="15" customHeight="1"/>
+    <row r="7" ht="15" customHeight="1"/>
+    <row r="8" ht="15" customHeight="1"/>
+    <row r="9" ht="15" customHeight="1"/>
+    <row r="10" ht="15" customHeight="1"/>
+    <row r="11" ht="15" customHeight="1"/>
+    <row r="12" ht="15" customHeight="1"/>
+    <row r="13" ht="15" customHeight="1"/>
+    <row r="14" ht="15" customHeight="1"/>
+    <row r="15" ht="15" customHeight="1"/>
+    <row r="16" ht="15" customHeight="1"/>
+    <row r="17" ht="15" customHeight="1"/>
+    <row r="18" ht="15" customHeight="1"/>
+    <row r="19" ht="15" customHeight="1"/>
+    <row r="20" ht="15" customHeight="1"/>
+    <row r="21" ht="15" customHeight="1"/>
+    <row r="22" ht="15" customHeight="1"/>
+    <row r="23" ht="15" customHeight="1"/>
+    <row r="24" ht="15" customHeight="1"/>
+    <row r="25" ht="15" customHeight="1"/>
+    <row r="26" ht="15" customHeight="1"/>
+    <row r="27" ht="15" customHeight="1"/>
+    <row r="28" ht="15" customHeight="1"/>
+    <row r="29" ht="15" customHeight="1"/>
+    <row r="30" ht="15" customHeight="1"/>
+    <row r="31" ht="15" customHeight="1"/>
+    <row r="32" ht="15" customHeight="1"/>
+    <row r="33" ht="15" customHeight="1"/>
+    <row r="34" ht="15" customHeight="1"/>
+    <row r="35" ht="15" customHeight="1"/>
+    <row r="36" ht="15" customHeight="1"/>
+    <row r="37" ht="15" customHeight="1"/>
+    <row r="38" ht="15" customHeight="1"/>
+    <row r="39" ht="15" customHeight="1"/>
+    <row r="40" ht="15" customHeight="1"/>
+    <row r="41" ht="15" customHeight="1"/>
+    <row r="42" ht="15" customHeight="1"/>
+    <row r="43" ht="15" customHeight="1"/>
+    <row r="44" ht="15" customHeight="1"/>
+    <row r="45" ht="15" customHeight="1"/>
+    <row r="46" ht="15" customHeight="1"/>
+    <row r="47" ht="15" customHeight="1"/>
+    <row r="48" ht="15" customHeight="1"/>
+    <row r="49" ht="15" customHeight="1"/>
+    <row r="50" ht="15" customHeight="1"/>
+    <row r="51" ht="15" customHeight="1"/>
+    <row r="52" ht="15" customHeight="1"/>
+    <row r="53" ht="15" customHeight="1"/>
+    <row r="54" ht="15" customHeight="1"/>
+    <row r="55" ht="15" customHeight="1"/>
+    <row r="56" ht="15" customHeight="1"/>
+    <row r="57" ht="15" customHeight="1"/>
+    <row r="58" ht="15" customHeight="1"/>
+    <row r="59" ht="15" customHeight="1"/>
+    <row r="60" ht="15" customHeight="1"/>
+    <row r="61" ht="15" customHeight="1"/>
+    <row r="62" ht="15" customHeight="1"/>
+    <row r="63" ht="15" customHeight="1"/>
+    <row r="64" ht="15" customHeight="1"/>
+    <row r="65" ht="15" customHeight="1"/>
+    <row r="66" ht="15" customHeight="1"/>
+    <row r="67" ht="15" customHeight="1"/>
+    <row r="68" ht="15" customHeight="1"/>
+    <row r="69" ht="15" customHeight="1"/>
+    <row r="70" ht="15" customHeight="1"/>
+    <row r="71" ht="15" customHeight="1"/>
+    <row r="72" ht="15" customHeight="1"/>
+    <row r="73" ht="15" customHeight="1"/>
+    <row r="74" ht="15" customHeight="1"/>
+    <row r="75" ht="15" customHeight="1"/>
+    <row r="76" ht="15" customHeight="1"/>
+    <row r="77" ht="15" customHeight="1"/>
+    <row r="78" ht="15" customHeight="1"/>
+    <row r="79" ht="15" customHeight="1"/>
+    <row r="80" ht="15" customHeight="1"/>
+    <row r="81" ht="15" customHeight="1"/>
+    <row r="82" ht="15" customHeight="1"/>
+    <row r="83" ht="15" customHeight="1"/>
+    <row r="84" ht="15" customHeight="1"/>
+    <row r="85" ht="15" customHeight="1"/>
+    <row r="86" ht="15" customHeight="1"/>
+    <row r="87" ht="15" customHeight="1"/>
+    <row r="88" ht="15" customHeight="1"/>
+    <row r="89" ht="15" customHeight="1"/>
+    <row r="90" ht="15" customHeight="1"/>
+    <row r="91" ht="15" customHeight="1"/>
+    <row r="92" ht="15" customHeight="1"/>
+    <row r="93" ht="15" customHeight="1"/>
+    <row r="94" ht="15" customHeight="1"/>
+    <row r="95" ht="15" customHeight="1"/>
+    <row r="96" ht="15" customHeight="1"/>
+    <row r="97" ht="15" customHeight="1"/>
+    <row r="98" ht="15" customHeight="1"/>
+    <row r="99" ht="15" customHeight="1"/>
+    <row r="100" ht="15" customHeight="1"/>
+    <row r="101" ht="15" customHeight="1"/>
+    <row r="102" ht="15" customHeight="1"/>
+    <row r="103" ht="15" customHeight="1"/>
+    <row r="104" ht="15" customHeight="1"/>
+    <row r="105" ht="15" customHeight="1"/>
+    <row r="106" ht="15" customHeight="1"/>
+    <row r="107" ht="15" customHeight="1"/>
+    <row r="108" ht="15" customHeight="1"/>
+    <row r="109" ht="15" customHeight="1"/>
+    <row r="110" ht="15" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1,29 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180" tabRatio="500"/>
+    <workbookView windowWidth="27795" windowHeight="12540" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="1" r:id="rId1"/>
     <sheet name="Planilha3" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -45,13 +32,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;* #,##0_-;\-&quot;R$&quot;* #,##0_-;_-&quot;R$&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="176" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;* #,##0_-;\-&quot;R$&quot;* #,##0_-;_-&quot;R$&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -80,31 +67,44 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -126,6 +126,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -135,7 +166,23 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -144,66 +191,20 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -211,21 +212,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,187 +227,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,17 +421,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -454,15 +435,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -478,6 +450,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -515,19 +498,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -536,154 +523,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -696,63 +677,60 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Moeda" xfId="2" builtinId="4"/>
-    <cellStyle name="Porcentagem" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Moeda [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Hyperlink seguido" xfId="7" builtinId="9"/>
-    <cellStyle name="Observação" xfId="8" builtinId="10"/>
-    <cellStyle name="Texto de Aviso" xfId="9" builtinId="11"/>
-    <cellStyle name="Título" xfId="10" builtinId="15"/>
-    <cellStyle name="Texto Explicativo" xfId="11" builtinId="53"/>
-    <cellStyle name="Título 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Título 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Título 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Título 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Entrada" xfId="16" builtinId="20"/>
-    <cellStyle name="Saída" xfId="17" builtinId="21"/>
-    <cellStyle name="Cálculo" xfId="18" builtinId="22"/>
-    <cellStyle name="Célula de Verificação" xfId="19" builtinId="23"/>
-    <cellStyle name="Célula Vinculada" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Bom" xfId="22" builtinId="26"/>
+    <cellStyle name="60% - Ênfase 6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Ênfase 6" xfId="2" builtinId="51"/>
+    <cellStyle name="20% - Ênfase 6" xfId="3" builtinId="50"/>
+    <cellStyle name="40% - Ênfase 5" xfId="4" builtinId="47"/>
+    <cellStyle name="Ênfase 5" xfId="5" builtinId="45"/>
+    <cellStyle name="Ênfase 4" xfId="6" builtinId="41"/>
+    <cellStyle name="Título 4" xfId="7" builtinId="19"/>
+    <cellStyle name="60% - Ênfase 3" xfId="8" builtinId="40"/>
+    <cellStyle name="20% - Ênfase 3" xfId="9" builtinId="38"/>
+    <cellStyle name="Ênfase 3" xfId="10" builtinId="37"/>
+    <cellStyle name="Título 3" xfId="11" builtinId="18"/>
+    <cellStyle name="60% - Ênfase 2" xfId="12" builtinId="36"/>
+    <cellStyle name="Célula de Verificação" xfId="13" builtinId="23"/>
+    <cellStyle name="40% - Ênfase 2" xfId="14" builtinId="35"/>
+    <cellStyle name="60% - Ênfase 5" xfId="15" builtinId="48"/>
+    <cellStyle name="Ênfase 2" xfId="16" builtinId="33"/>
+    <cellStyle name="Ênfase 6" xfId="17" builtinId="49"/>
+    <cellStyle name="40% - Ênfase 1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Ênfase 1" xfId="19" builtinId="30"/>
+    <cellStyle name="60% - Ênfase 4" xfId="20" builtinId="44"/>
+    <cellStyle name="Ênfase 1" xfId="21" builtinId="29"/>
+    <cellStyle name="40% - Ênfase 4" xfId="22" builtinId="43"/>
     <cellStyle name="Ruim" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutro" xfId="24" builtinId="28"/>
-    <cellStyle name="Ênfase 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Ênfase 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Ênfase 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Ênfase 1" xfId="28" builtinId="32"/>
-    <cellStyle name="Ênfase 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Ênfase 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Ênfase 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Ênfase 2" xfId="32" builtinId="36"/>
-    <cellStyle name="Ênfase 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Ênfase 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Ênfase 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Ênfase 3" xfId="36" builtinId="40"/>
-    <cellStyle name="Ênfase 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Ênfase 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Ênfase 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Ênfase 4" xfId="40" builtinId="44"/>
-    <cellStyle name="Ênfase 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Ênfase 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Ênfase 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Ênfase 5" xfId="44" builtinId="48"/>
-    <cellStyle name="Ênfase 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Ênfase 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Ênfase 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Ênfase 6" xfId="48" builtinId="52"/>
+    <cellStyle name="20% - Ênfase 4" xfId="24" builtinId="42"/>
+    <cellStyle name="Saída" xfId="25" builtinId="21"/>
+    <cellStyle name="Hyperlink seguido" xfId="26" builtinId="9"/>
+    <cellStyle name="Moeda [0]" xfId="27" builtinId="7"/>
+    <cellStyle name="Total" xfId="28" builtinId="25"/>
+    <cellStyle name="Bom" xfId="29" builtinId="26"/>
+    <cellStyle name="40% - Ênfase 3" xfId="30" builtinId="39"/>
+    <cellStyle name="Texto de Aviso" xfId="31" builtinId="11"/>
+    <cellStyle name="Cálculo" xfId="32" builtinId="22"/>
+    <cellStyle name="Entrada" xfId="33" builtinId="20"/>
+    <cellStyle name="Texto Explicativo" xfId="34" builtinId="53"/>
+    <cellStyle name="Título 1" xfId="35" builtinId="16"/>
+    <cellStyle name="Título" xfId="36" builtinId="15"/>
+    <cellStyle name="Observação" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - Ênfase 2" xfId="38" builtinId="34"/>
+    <cellStyle name="60% - Ênfase 1" xfId="39" builtinId="32"/>
+    <cellStyle name="Título 2" xfId="40" builtinId="17"/>
+    <cellStyle name="Hyperlink" xfId="41" builtinId="8"/>
+    <cellStyle name="Célula Vinculada" xfId="42" builtinId="24"/>
+    <cellStyle name="Comma" xfId="43" builtinId="3"/>
+    <cellStyle name="Porcentagem" xfId="44" builtinId="5"/>
+    <cellStyle name="Neutro" xfId="45" builtinId="28"/>
+    <cellStyle name="20% - Ênfase 5" xfId="46" builtinId="46"/>
+    <cellStyle name="Moeda" xfId="47" builtinId="4"/>
+    <cellStyle name="Comma [0]" xfId="48" builtinId="6"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -947,7 +925,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -956,7 +934,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1156,28 +1134,33 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelRow="1" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="18.8571428571429" style="6" customWidth="1"/>
-    <col min="2" max="2" width="15.1428571428571" style="7" customWidth="1"/>
-    <col min="3" max="3" width="18.8571428571429" style="7" customWidth="1"/>
+    <col min="1" max="1" width="22.1428571428571" style="4" customWidth="1"/>
+    <col min="2" max="2" width="18.1428571428571" style="5" customWidth="1"/>
+    <col min="3" max="3" width="22.7142857142857" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="2:3">
-      <c r="B2" s="6" t="str">
+    <row r="2" customHeight="1" spans="1:3">
+      <c r="A2" s="4">
+        <v>5000</v>
+      </c>
+      <c r="B2" s="4">
         <f>Planilha3!B1</f>
-        <v/>
+        <v>365</v>
       </c>
-      <c r="C2" s="9"/>
+      <c r="C2" s="6">
+        <v>46082</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -1195,25 +1178,39 @@
   <dimension ref="A1:B110"/>
   <sheetFormatPr defaultColWidth="12.6761904761905" defaultRowHeight="12.8" customHeight="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.1428571428571" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.14285714285714" style="2" customWidth="1"/>
+    <col min="1" max="1" width="18.7142857142857" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" spans="1:2">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="20.25" spans="1:2">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="4" t="str">
+      <c r="B1" s="2">
         <f>IF(A2="","",SUM(A2:A54))</f>
-        <v/>
+        <v>365</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:1">
-      <c r="A2" s="5"/>
+      <c r="A2" s="3">
+        <v>35</v>
+      </c>
     </row>
-    <row r="3" ht="15" customHeight="1"/>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="5" ht="15" customHeight="1"/>
+    <row r="3" ht="15" customHeight="1" spans="1:1">
+      <c r="A3" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:1">
+      <c r="A4" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:1">
+      <c r="A5" s="1">
+        <v>180</v>
+      </c>
+    </row>
     <row r="6" ht="15" customHeight="1"/>
     <row r="7" ht="15" customHeight="1"/>
     <row r="8" ht="15" customHeight="1"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -1161,9 +1161,12 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:3">
-      <c r="B2" s="3" t="str">
+      <c r="A2" s="3">
+        <v>9944</v>
+      </c>
+      <c r="B2" s="3">
         <f>Planilha3!B1</f>
-        <v/>
+        <v>2115</v>
       </c>
       <c r="C2" s="5">
         <v>46226</v>
@@ -1193,13 +1196,15 @@
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="str">
+      <c r="B1" s="1">
         <f>IF(A2="","",SUM(A2:A54))</f>
-        <v/>
+        <v>2115</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:2">
-      <c r="A2" s="2"/>
+      <c r="A2" s="2">
+        <v>2115</v>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="4" ht="15" customHeight="1"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180" tabRatio="500"/>
+    <workbookView windowWidth="27945" windowHeight="11580" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="1" r:id="rId1"/>
@@ -1162,11 +1162,11 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:3">
       <c r="A2" s="3">
-        <v>9944</v>
+        <v>10159</v>
       </c>
       <c r="B2" s="3">
         <f>Planilha3!B1</f>
-        <v>2115</v>
+        <v>2192</v>
       </c>
       <c r="C2" s="5">
         <v>46226</v>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B1" s="1">
         <f>IF(A2="","",SUM(A2:A54))</f>
-        <v>2115</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:2">
       <c r="A2" s="2">
-        <v>2115</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11580" tabRatio="500"/>
+    <workbookView windowWidth="27945" windowHeight="12180" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="1" r:id="rId1"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180" tabRatio="500"/>
+    <workbookView windowWidth="27945" windowHeight="12180" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="1" r:id="rId1"/>
@@ -1149,7 +1149,7 @@
     <col min="3" max="3" width="22.7142857142857" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:3">
+    <row r="1" ht="30" customHeight="1" spans="1:3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B2" s="3">
         <f>Planilha3!B1</f>
-        <v>2192</v>
+        <v>2263</v>
       </c>
       <c r="C2" s="5">
         <v>46226</v>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B1" s="1">
         <f>IF(A2="","",SUM(A2:A54))</f>
-        <v>2192</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:2">
       <c r="A2" s="2">
-        <v>2192</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12180" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="1" r:id="rId1"/>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:3">
       <c r="A2" s="3">
-        <v>10159</v>
+        <v>10790</v>
       </c>
       <c r="B2" s="3">
         <f>Planilha3!B1</f>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1162,7 +1162,7 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:3">
       <c r="A2" s="3">
-        <v>10790</v>
+        <v>10159</v>
       </c>
       <c r="B2" s="3">
         <f>Planilha3!B1</f>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180" tabRatio="500"/>
+    <workbookView windowWidth="27945" windowHeight="12180" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="1" r:id="rId1"/>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B2" s="3">
         <f>Planilha3!B1</f>
-        <v>2263</v>
+        <v>2335</v>
       </c>
       <c r="C2" s="5">
         <v>46226</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B1" s="1">
         <f>IF(A2="","",SUM(A2:A54))</f>
-        <v>2263</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:2">
@@ -1206,7 +1206,11 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1"/>
+    <row r="3" ht="15" customHeight="1" spans="1:2">
+      <c r="A3" s="1">
+        <v>72</v>
+      </c>
+    </row>
     <row r="4" ht="15" customHeight="1"/>
     <row r="5" ht="15" customHeight="1"/>
     <row r="6" ht="15" customHeight="1"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B2" s="3">
         <f>Planilha3!B1</f>
-        <v>2335</v>
+        <v>2348</v>
       </c>
       <c r="C2" s="5">
         <v>46226</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B1" s="1">
         <f>IF(A2="","",SUM(A2:A54))</f>
-        <v>2335</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:2">
@@ -1211,7 +1211,11 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1"/>
+    <row r="4" ht="15" customHeight="1" spans="1:2">
+      <c r="A4" s="1">
+        <v>13</v>
+      </c>
+    </row>
     <row r="5" ht="15" customHeight="1"/>
     <row r="6" ht="15" customHeight="1"/>
     <row r="7" ht="15" customHeight="1"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B2" s="3">
         <f>Planilha3!B1</f>
-        <v>2348</v>
+        <v>2449</v>
       </c>
       <c r="C2" s="5">
         <v>46226</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B1" s="1">
         <f>IF(A2="","",SUM(A2:A54))</f>
-        <v>2348</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:2">
@@ -1216,8 +1216,16 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1"/>
-    <row r="6" ht="15" customHeight="1"/>
+    <row r="5" ht="15" customHeight="1" spans="1:2">
+      <c r="A5" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:2">
+      <c r="A6" s="1">
+        <v>59</v>
+      </c>
+    </row>
     <row r="7" ht="15" customHeight="1"/>
     <row r="8" ht="15" customHeight="1"/>
     <row r="9" ht="15" customHeight="1"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B2" s="3">
         <f>Planilha3!B1</f>
-        <v>2449</v>
+        <v>2543</v>
       </c>
       <c r="C2" s="5">
         <v>46226</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B1" s="1">
         <f>IF(A2="","",SUM(A2:A54))</f>
-        <v>2449</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:2">
@@ -1226,8 +1226,16 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1"/>
-    <row r="8" ht="15" customHeight="1"/>
+    <row r="7" ht="15" customHeight="1" spans="1:2">
+      <c r="A7" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:2">
+      <c r="A8" s="1">
+        <v>50</v>
+      </c>
+    </row>
     <row r="9" ht="15" customHeight="1"/>
     <row r="10" ht="15" customHeight="1"/>
     <row r="11" ht="15" customHeight="1"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B2" s="3">
         <f>Planilha3!B1</f>
-        <v>2543</v>
+        <v>2630</v>
       </c>
       <c r="C2" s="5">
         <v>46226</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B1" s="1">
         <f>IF(A2="","",SUM(A2:A54))</f>
-        <v>2543</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:2">
@@ -1236,8 +1236,16 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1"/>
-    <row r="10" ht="15" customHeight="1"/>
+    <row r="9" ht="15" customHeight="1" spans="1:2">
+      <c r="A9" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:2">
+      <c r="A10" s="1">
+        <v>47</v>
+      </c>
+    </row>
     <row r="11" ht="15" customHeight="1"/>
     <row r="12" ht="15" customHeight="1"/>
     <row r="13" ht="15" customHeight="1"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B2" s="3">
         <f>Planilha3!B1</f>
-        <v>2630</v>
+        <v>2723</v>
       </c>
       <c r="C2" s="5">
         <v>46226</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B1" s="1">
         <f>IF(A2="","",SUM(A2:A54))</f>
-        <v>2630</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:2">
@@ -1246,8 +1246,16 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1"/>
-    <row r="12" ht="15" customHeight="1"/>
+    <row r="11" ht="15" customHeight="1" spans="1:2">
+      <c r="A11" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:2">
+      <c r="A12" s="1">
+        <v>45</v>
+      </c>
+    </row>
     <row r="13" ht="15" customHeight="1"/>
     <row r="14" ht="15" customHeight="1"/>
     <row r="15" ht="15" customHeight="1"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="13545" windowHeight="12180" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="1" r:id="rId1"/>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B2" s="3">
         <f>Planilha3!B1</f>
-        <v>2723</v>
+        <v>2812</v>
       </c>
       <c r="C2" s="5">
         <v>46226</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B1" s="1">
         <f>IF(A2="","",SUM(A2:A54))</f>
-        <v>2723</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:2">
@@ -1256,8 +1256,16 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1"/>
-    <row r="14" ht="15" customHeight="1"/>
+    <row r="13" ht="15" customHeight="1" spans="1:2">
+      <c r="A13" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:2">
+      <c r="A14" s="1">
+        <v>45</v>
+      </c>
+    </row>
     <row r="15" ht="15" customHeight="1"/>
     <row r="16" ht="15" customHeight="1"/>
     <row r="17" ht="15" customHeight="1"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12180" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12180" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="1" r:id="rId1"/>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B2" s="3">
         <f>Planilha3!B1</f>
-        <v>2812</v>
+        <v>2898</v>
       </c>
       <c r="C2" s="5">
         <v>46226</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B1" s="1">
         <f>IF(A2="","",SUM(A2:A54))</f>
-        <v>2812</v>
+        <v>2898</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:2">
@@ -1266,8 +1266,16 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1"/>
-    <row r="16" ht="15" customHeight="1"/>
+    <row r="15" ht="15" customHeight="1" spans="1:2">
+      <c r="A15" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:2">
+      <c r="A16" s="1">
+        <v>42</v>
+      </c>
+    </row>
     <row r="17" ht="15" customHeight="1"/>
     <row r="18" ht="15" customHeight="1"/>
     <row r="19" ht="15" customHeight="1"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B2" s="3">
         <f>Planilha3!B1</f>
-        <v>2898</v>
+        <v>2943</v>
       </c>
       <c r="C2" s="5">
         <v>46226</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B1" s="1">
         <f>IF(A2="","",SUM(A2:A54))</f>
-        <v>2898</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:2">
@@ -1276,8 +1276,16 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1"/>
-    <row r="18" ht="15" customHeight="1"/>
+    <row r="17" ht="15" customHeight="1" spans="1:1">
+      <c r="A17" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:1">
+      <c r="A18" s="1">
+        <v>39</v>
+      </c>
+    </row>
     <row r="19" ht="15" customHeight="1"/>
     <row r="20" ht="15" customHeight="1"/>
     <row r="21" ht="15" customHeight="1"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B2" s="3">
         <f>Planilha3!B1</f>
-        <v>2943</v>
+        <v>3014</v>
       </c>
       <c r="C2" s="5">
         <v>46226</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B1" s="1">
         <f>IF(A2="","",SUM(A2:A54))</f>
-        <v>2943</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:2">
@@ -1286,8 +1286,16 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1"/>
-    <row r="20" ht="15" customHeight="1"/>
+    <row r="19" ht="15" customHeight="1" spans="1:1">
+      <c r="A19" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:1">
+      <c r="A20" s="1">
+        <v>28</v>
+      </c>
+    </row>
     <row r="21" ht="15" customHeight="1"/>
     <row r="22" ht="15" customHeight="1"/>
     <row r="23" ht="15" customHeight="1"/>

--- a/TesteOdair.xlsx
+++ b/TesteOdair.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B2" s="3">
         <f>Planilha3!B1</f>
-        <v>3014</v>
+        <v>3103</v>
       </c>
       <c r="C2" s="5">
         <v>46226</v>
@@ -1197,8 +1197,8 @@
         <v>3</v>
       </c>
       <c r="B1" s="1">
-        <f>IF(A2="","",SUM(A2:A54))</f>
-        <v>3014</v>
+        <f>IF(A2="","",SUM(A2:A122))</f>
+        <v>3103</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:2">
@@ -1296,8 +1296,16 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1"/>
-    <row r="22" ht="15" customHeight="1"/>
+    <row r="21" ht="15" customHeight="1" spans="1:1">
+      <c r="A21" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:1">
+      <c r="A22" s="1">
+        <v>43</v>
+      </c>
+    </row>
     <row r="23" ht="15" customHeight="1"/>
     <row r="24" ht="15" customHeight="1"/>
     <row r="25" ht="15" customHeight="1"/>
